--- a/data/nse/delivery/daily_output/delivery_breakout_20260714.xlsx
+++ b/data/nse/delivery/daily_output/delivery_breakout_20260714.xlsx
@@ -504,10 +504,10 @@
         <v>50.62</v>
       </c>
       <c r="F2" t="n">
-        <v>501410.3333333333</v>
+        <v>488906.7586206897</v>
       </c>
       <c r="G2" t="n">
-        <v>7.16</v>
+        <v>7.34</v>
       </c>
       <c r="H2" t="n">
         <v>453.09</v>
@@ -534,10 +534,10 @@
         <v>6.52</v>
       </c>
       <c r="F3" t="n">
-        <v>133014.6333333333</v>
+        <v>136325.0689655172</v>
       </c>
       <c r="G3" t="n">
-        <v>20.88</v>
+        <v>20.37</v>
       </c>
       <c r="H3" t="n">
         <v>3363.62</v>
@@ -564,7 +564,7 @@
         <v>76.61</v>
       </c>
       <c r="F4" t="n">
-        <v>135479</v>
+        <v>135699.724137931</v>
       </c>
       <c r="G4" t="n">
         <v>5.49</v>
@@ -594,10 +594,10 @@
         <v>8.359999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>137704.7333333333</v>
+        <v>139220.6896551724</v>
       </c>
       <c r="G5" t="n">
-        <v>12.83</v>
+        <v>12.69</v>
       </c>
       <c r="H5" t="n">
         <v>721.51</v>
@@ -624,10 +624,10 @@
         <v>18.27</v>
       </c>
       <c r="F6" t="n">
-        <v>127418.9</v>
+        <v>130170.1379310345</v>
       </c>
       <c r="G6" t="n">
-        <v>7.12</v>
+        <v>6.97</v>
       </c>
       <c r="H6" t="n">
         <v>299.58</v>
